--- a/218/food/findex.xlsx
+++ b/218/food/findex.xlsx
@@ -1,221 +1,95 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54051FC5-41A7-4AB9-B9E3-BE5733879C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="162913" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
-  <si>
-    <t>Школа</t>
-  </si>
-  <si>
-    <t>Перечень ресурсов раздела Питание</t>
-  </si>
-  <si>
-    <t>№</t>
-  </si>
-  <si>
-    <t>Наименование</t>
-  </si>
-  <si>
-    <t>Примечание</t>
-  </si>
-  <si>
-    <t>Положение и приказ о создании комиссии по контролю качества питания с участием родителей</t>
-  </si>
-  <si>
-    <t>Интернет-ссылка</t>
-  </si>
-  <si>
-    <t>Формы интерактивного взаимодействия с родителями</t>
-  </si>
-  <si>
-    <t>Форум</t>
-  </si>
-  <si>
-    <t>Чат</t>
-  </si>
-  <si>
-    <t>Наличие лечебных/диетических меню</t>
-  </si>
-  <si>
-    <t>"Горячая линия"</t>
-  </si>
-  <si>
-    <t>вид</t>
-  </si>
-  <si>
-    <t>ссылка на файл меню</t>
-  </si>
-  <si>
-    <t>Проведение регулярного анкетирования обучающихся и родителей по питанию</t>
-  </si>
-  <si>
-    <t>Наличие информации для родителей о здоровом питании, размещенной на сайте образовательной организации</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Файл с информационными материалами </t>
-  </si>
-  <si>
-    <t>(буклет, брошюра, листовка и т.п.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Информация по результатам контрольных мероприятий с участием родителей. </t>
-  </si>
-  <si>
-    <t>Файл с результатами (актами) проверок</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Файл(ы) фото членов комиссии при проверке </t>
-  </si>
-  <si>
-    <t>Фото членов комиссии в школьной столовой при проверке (jpeg, png)</t>
-  </si>
-  <si>
-    <t>20 % и менее</t>
-  </si>
-  <si>
-    <t>50 % и более</t>
-  </si>
-  <si>
-    <t>Отметить "+" наиболее подходящий ответ</t>
-  </si>
-  <si>
-    <t>Не ведется</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Файл с результатами </t>
-  </si>
-  <si>
-    <t>Акты/протоколы проверок (не реже раза в месяц).Допустимы документы об участии родителей в регулярном бракераже блюд и сырья</t>
-  </si>
-  <si>
-    <t>Телефон, е-мейл и т.п.</t>
-  </si>
-  <si>
-    <t>Интернет-ссылка на файл на сайте школы</t>
-  </si>
-  <si>
-    <t>Например: антиаллергенное, диабетическое, безлактозное и т.п.</t>
-  </si>
-  <si>
-    <t>Ссылка на файл на сайте</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ссылка на страницу мероприятия на сайте </t>
-  </si>
-  <si>
-    <t>дд.мм.гггг</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ссылка на форму анкеты </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Оценка количества пищевых отходов или объема несъедаемых блюд </t>
-  </si>
-  <si>
-    <t>Адрес на сайте школы</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="8">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="8"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
-      <b/>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
-      <i/>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <i val="1"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
     <font>
-      <b/>
-      <i/>
+      <name val="Arial"/>
+      <charset val="204"/>
+      <family val="2"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,148 +266,214 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="43">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -799,329 +739,433 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26.140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="56" style="1" customWidth="1"/>
-    <col min="4" max="4" width="45" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col width="6.5703125" customWidth="1" style="1" min="1" max="1"/>
+    <col width="26.140625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="56" customWidth="1" style="1" min="3" max="3"/>
+    <col width="45" customWidth="1" style="2" min="4" max="4"/>
+    <col width="9.140625" customWidth="1" style="1" min="5" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="40"/>
-      <c r="D1" s="38" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Школа</t>
+        </is>
+      </c>
+      <c r="B1" s="41" t="n"/>
+      <c r="C1" s="42" t="n"/>
+      <c r="D1" s="38" t="inlineStr">
+        <is>
+          <t>дд.мм.гггг</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Перечень ресурсов раздела Питание</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="11.25" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Наименование</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Адрес на сайте школы</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Примечание</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="51" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Положение и приказ о создании комиссии по контролю качества питания с участием родителей</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="n"/>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>Интернет-ссылка на файл на сайте школы</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B5" s="17" t="inlineStr">
+        <is>
+          <t>Формы интерактивного взаимодействия с родителями</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>"Горячая линия"</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="n"/>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>Телефон, е-мейл и т.п.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Чат</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="n"/>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Интернет-ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>Форум</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="33" t="inlineStr">
+        <is>
+          <t>Интернет-ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>Наличие лечебных/диетических меню</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="34" t="n"/>
+    </row>
+    <row r="10" ht="25.5" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>вид</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>Например: антиаллергенное, диабетическое, безлактозное и т.п.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>ссылка на файл меню</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="33" t="inlineStr">
+        <is>
+          <t>Интернет-ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="21" t="inlineStr">
+        <is>
+          <t>вид</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="31" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>ссылка на файл меню</t>
+        </is>
+      </c>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Интернет-ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>вид</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="32" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>ссылка на файл меню</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="33" t="inlineStr">
+        <is>
+          <t>Интернет-ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>вид</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="31" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>ссылка на файл меню</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="33" t="inlineStr">
+        <is>
+          <t>Интернет-ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="51" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
-        <v>1</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Проведение регулярного анкетирования обучающихся и родителей по питанию</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="35" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ссылка на форму анкеты </t>
+        </is>
+      </c>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Интернет-ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Файл с результатами </t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Ссылка на файл на сайте</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="13"/>
-      <c r="D4" s="30" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>2</v>
-      </c>
-      <c r="B5" s="17" t="s">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>Наличие информации для родителей о здоровом питании, размещенной на сайте образовательной организации</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="34" t="n"/>
+    </row>
+    <row r="22" ht="25.5" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ссылка на страницу мероприятия на сайте </t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>Интернет-ссылка</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25.5" customHeight="1">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Файл с информационными материалами </t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>(буклет, брошюра, листовка и т.п.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Информация по результатам контрольных мероприятий с участием родителей. </t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="34" t="n"/>
+    </row>
+    <row r="25" ht="42.75" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Файл с результатами (актами) проверок</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="36" t="inlineStr">
+        <is>
+          <t>Акты/протоколы проверок (не реже раза в месяц).Допустимы документы об участии родителей в регулярном бракераже блюд и сырья</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="25.5" customHeight="1">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Файл(ы) фото членов комиссии при проверке </t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="30" t="inlineStr">
+        <is>
+          <t>Фото членов комиссии в школьной столовой при проверке (jpeg, png)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="D5" s="31"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="32" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="21" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="6"/>
-      <c r="B8" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>3</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="34"/>
-    </row>
-    <row r="10" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="31"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="32"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="14"/>
-      <c r="D16" s="31"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="33" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>4</v>
-      </c>
-      <c r="B18" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="35"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="14"/>
-      <c r="D19" s="31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="13"/>
-      <c r="D20" s="31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="5">
-        <v>5</v>
-      </c>
-      <c r="B21" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="11"/>
-      <c r="D21" s="34"/>
-    </row>
-    <row r="22" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="31" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
-        <v>6</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="34"/>
-    </row>
-    <row r="25" spans="1:4" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="36" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="C26" s="13"/>
-      <c r="D26" s="30" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="5">
-        <v>7</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="11"/>
-      <c r="D27" s="34"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="37" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="28">
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Оценка количества пищевых отходов или объема несъедаемых блюд </t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="34" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="27" t="inlineStr">
+        <is>
+          <t>20 % и менее</t>
+        </is>
+      </c>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="37" t="inlineStr">
+        <is>
+          <t>Отметить "+" наиболее подходящий ответ</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="28" t="n">
         <v>0.3</v>
       </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="37"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="28">
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="37" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="28" t="n">
         <v>0.4</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="37"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="37"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="6"/>
-      <c r="B32" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="C32" s="13"/>
-      <c r="D32" s="36"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="37" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="27" t="inlineStr">
+        <is>
+          <t>50 % и более</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="37" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="29" t="inlineStr">
+        <is>
+          <t>Не ведется</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="36" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="1" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="1" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="B1:C1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>